--- a/research/traditional_assets/database/data/new_zealand/new_zealand_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_investments_asset_management.xlsx
@@ -588,40 +588,40 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.01980815435687691</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>-0.01980815435687691</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>0.9009042055646241</v>
+        <v>-118.764705882353</v>
       </c>
       <c r="J2">
-        <v>0.8862803096426333</v>
+        <v>-118.764705882353</v>
       </c>
       <c r="K2">
-        <v>47.2</v>
+        <v>-37.79</v>
       </c>
       <c r="L2">
-        <v>0.8656897089301762</v>
+        <v>-116.9969040247678</v>
       </c>
       <c r="M2">
-        <v>6.7</v>
+        <v>7.17</v>
       </c>
       <c r="N2">
-        <v>0.03302444794952681</v>
+        <v>0.05950701303012697</v>
       </c>
       <c r="O2">
-        <v>0.1419491525423729</v>
+        <v>-0.1897327335273882</v>
       </c>
       <c r="P2">
-        <v>6.7</v>
+        <v>7.17</v>
       </c>
       <c r="Q2">
-        <v>0.03302444794952681</v>
+        <v>0.05950701303012697</v>
       </c>
       <c r="R2">
-        <v>0.1419491525423729</v>
+        <v>-0.1897327335273882</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -630,31 +630,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>6.92</v>
+        <v>4.390000000000001</v>
       </c>
       <c r="V2">
-        <v>0.03410883280757097</v>
+        <v>0.03643455888455473</v>
       </c>
       <c r="W2">
-        <v>0.09291666666666665</v>
+        <v>-0.1265786069450621</v>
       </c>
       <c r="X2">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y2">
-        <v>0.04904370257518437</v>
+        <v>-0.1990328259857669</v>
       </c>
       <c r="Z2">
-        <v>0.5346650192202087</v>
+        <v>0.001905829596412556</v>
       </c>
       <c r="AA2">
-        <v>0.0572960350710586</v>
+        <v>-0.1675281467872621</v>
       </c>
       <c r="AB2">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC2">
-        <v>0.01342307097957632</v>
+        <v>-0.239982365827967</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -666,7 +666,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-6.92</v>
+        <v>-4.390000000000001</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -675,28 +675,16 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.03531332925086752</v>
+        <v>-0.03781223083548665</v>
       </c>
       <c r="AK2">
-        <v>-0.04083077649280151</v>
+        <v>-0.03878777169111151</v>
       </c>
       <c r="AL2">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>0.001</v>
-      </c>
-      <c r="AN2">
-        <v>-0</v>
-      </c>
-      <c r="AO2">
-        <v>49120</v>
-      </c>
-      <c r="AP2">
-        <v>6.407407407407407</v>
-      </c>
-      <c r="AQ2">
-        <v>49120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +695,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Marlin Global Limited (NZSE:MLN)</t>
+          <t>Powerhouse Ventures Limited (ASX:PVL)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,67 +710,64 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.9177330895795247</v>
+        <v>-0.8080495356037152</v>
       </c>
       <c r="J3">
-        <v>0.8879389491963817</v>
+        <v>-0.8080495356037152</v>
       </c>
       <c r="K3">
-        <v>48.3</v>
+        <v>-0.19</v>
       </c>
       <c r="L3">
-        <v>0.882998171846435</v>
+        <v>-0.5882352941176471</v>
       </c>
       <c r="M3">
-        <v>6.7</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.03430619559651817</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.1387163561076605</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>6.7</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.03430619559651817</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.1387163561076605</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>3.56</v>
+        <v>2.77</v>
       </c>
       <c r="V3">
-        <v>0.01822836661546339</v>
+        <v>0.6456876456876457</v>
       </c>
       <c r="W3">
-        <v>0.4791666666666666</v>
+        <v>-0.03275862068965518</v>
       </c>
       <c r="X3">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y3">
-        <v>0.4352937025751843</v>
+        <v>-0.10521283973036</v>
       </c>
       <c r="Z3">
-        <v>0.5519677093844602</v>
+        <v>0.1323770491803279</v>
       </c>
       <c r="AA3">
-        <v>0.4901136278611715</v>
+        <v>-0.1069672131147541</v>
       </c>
       <c r="AB3">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC3">
-        <v>0.4462406637696892</v>
+        <v>-0.179421432155459</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -794,7 +779,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-3.56</v>
+        <v>-2.77</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -803,10 +788,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.01856680922081986</v>
+        <v>-1.822368421052632</v>
       </c>
       <c r="AK3">
-        <v>-0.02131226053639847</v>
+        <v>-0.6925000000000001</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -823,7 +808,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Powerhouse Ventures Limited (ASX:PVL)</t>
+          <t>Marlin Global Limited (NZSE:MLN)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -831,71 +816,59 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G4">
-        <v>6.101694915254238</v>
-      </c>
-      <c r="H4">
-        <v>6.101694915254238</v>
-      </c>
-      <c r="I4">
-        <v>6.101694915254238</v>
-      </c>
-      <c r="J4">
-        <v>6.101694915254238</v>
-      </c>
       <c r="K4">
-        <v>-1.1</v>
-      </c>
-      <c r="L4">
-        <v>6.214689265536724</v>
+        <v>-37.6</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>7.17</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.0617039586919105</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>-0.1906914893617021</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>7.17</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.0617039586919105</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>-0.1906914893617021</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>3.36</v>
+        <v>1.62</v>
       </c>
       <c r="V4">
-        <v>0.4432717678100264</v>
+        <v>0.01394148020654045</v>
       </c>
       <c r="W4">
-        <v>-0.2933333333333333</v>
+        <v>-0.220398593200469</v>
       </c>
       <c r="X4">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="Y4">
-        <v>-0.3372062974248156</v>
+        <v>-0.2928528122411738</v>
       </c>
       <c r="Z4">
-        <v>-0.06154381084840056</v>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>-0.3755215577190543</v>
+        <v>-0.2280890804597701</v>
       </c>
       <c r="AB4">
-        <v>0.04387296409148227</v>
+        <v>0.07245421904070486</v>
       </c>
       <c r="AC4">
-        <v>-0.4193945218105365</v>
+        <v>-0.300543299500475</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -907,7 +880,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-3.36</v>
+        <v>-1.62</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -916,28 +889,16 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.7962085308056871</v>
+        <v>-0.01413859312270902</v>
       </c>
       <c r="AK4">
-        <v>-1.377049180327869</v>
+        <v>-0.01483788239604323</v>
       </c>
       <c r="AL4">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>0.001</v>
-      </c>
-      <c r="AN4">
-        <v>-0</v>
-      </c>
-      <c r="AO4">
-        <v>-1080</v>
-      </c>
-      <c r="AP4">
-        <v>3.111111111111111</v>
-      </c>
-      <c r="AQ4">
-        <v>-1080</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/new_zealand/new_zealand_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,6 +587,12 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.00808</v>
+      </c>
+      <c r="E2">
+        <v>-0.00189</v>
+      </c>
       <c r="G2">
         <v>0</v>
       </c>
@@ -594,34 +600,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-118.764705882353</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="J2">
-        <v>-118.764705882353</v>
+        <v>0.8533951835767863</v>
       </c>
       <c r="K2">
-        <v>-37.79</v>
+        <v>14.5</v>
       </c>
       <c r="L2">
-        <v>-116.9969040247678</v>
+        <v>0.8529411764705882</v>
       </c>
       <c r="M2">
-        <v>7.17</v>
+        <v>5.46</v>
       </c>
       <c r="N2">
-        <v>0.05950701303012697</v>
+        <v>0.04292452830188679</v>
       </c>
       <c r="O2">
-        <v>-0.1897327335273882</v>
+        <v>0.376551724137931</v>
       </c>
       <c r="P2">
-        <v>7.17</v>
+        <v>5.46</v>
       </c>
       <c r="Q2">
-        <v>0.05950701303012697</v>
+        <v>0.04292452830188679</v>
       </c>
       <c r="R2">
-        <v>-0.1897327335273882</v>
+        <v>0.376551724137931</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -630,31 +636,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>4.390000000000001</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="V2">
-        <v>0.03643455888455473</v>
+        <v>0.07822327044025157</v>
       </c>
       <c r="W2">
-        <v>-0.1265786069450621</v>
+        <v>0.1308664259927798</v>
       </c>
       <c r="X2">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y2">
-        <v>-0.1990328259857669</v>
+        <v>0.06855803745697815</v>
       </c>
       <c r="Z2">
-        <v>0.001905829596412556</v>
+        <v>0.1557061732918117</v>
       </c>
       <c r="AA2">
-        <v>-0.1675281467872621</v>
+        <v>0.1328788983404046</v>
       </c>
       <c r="AB2">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC2">
-        <v>-0.239982365827967</v>
+        <v>0.07057050980460293</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -666,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-4.390000000000001</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -675,10 +681,10 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.03781223083548665</v>
+        <v>-0.08486140724946695</v>
       </c>
       <c r="AK2">
-        <v>-0.03878777169111151</v>
+        <v>-0.09200184928340269</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -695,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Powerhouse Ventures Limited (ASX:PVL)</t>
+          <t>Marlin Global Limited (NZSE:MLN)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -703,6 +709,12 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.00808</v>
+      </c>
+      <c r="E3">
+        <v>-0.00189</v>
+      </c>
       <c r="G3">
         <v>0</v>
       </c>
@@ -710,64 +722,67 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-0.8080495356037152</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="J3">
-        <v>-0.8080495356037152</v>
+        <v>0.8533951835767863</v>
       </c>
       <c r="K3">
-        <v>-0.19</v>
+        <v>14.5</v>
       </c>
       <c r="L3">
-        <v>-0.5882352941176471</v>
+        <v>0.8529411764705882</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>5.46</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.04292452830188679</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.376551724137931</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>5.46</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.04292452830188679</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>0.376551724137931</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>2.77</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="V3">
-        <v>0.6456876456876457</v>
+        <v>0.07822327044025157</v>
       </c>
       <c r="W3">
-        <v>-0.03275862068965518</v>
+        <v>0.1308664259927798</v>
       </c>
       <c r="X3">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="Y3">
-        <v>-0.10521283973036</v>
+        <v>0.06855803745697815</v>
       </c>
       <c r="Z3">
-        <v>0.1323770491803279</v>
+        <v>0.1557061732918117</v>
       </c>
       <c r="AA3">
-        <v>-0.1069672131147541</v>
+        <v>0.1328788983404046</v>
       </c>
       <c r="AB3">
-        <v>0.07245421904070486</v>
+        <v>0.06230838853580163</v>
       </c>
       <c r="AC3">
-        <v>-0.179421432155459</v>
+        <v>0.07057050980460293</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -779,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-2.77</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -788,116 +803,15 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-1.822368421052632</v>
+        <v>-0.08486140724946695</v>
       </c>
       <c r="AK3">
-        <v>-0.6925000000000001</v>
+        <v>-0.09200184928340269</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Marlin Global Limited (NZSE:MLN)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K4">
-        <v>-37.6</v>
-      </c>
-      <c r="M4">
-        <v>7.17</v>
-      </c>
-      <c r="N4">
-        <v>0.0617039586919105</v>
-      </c>
-      <c r="O4">
-        <v>-0.1906914893617021</v>
-      </c>
-      <c r="P4">
-        <v>7.17</v>
-      </c>
-      <c r="Q4">
-        <v>0.0617039586919105</v>
-      </c>
-      <c r="R4">
-        <v>-0.1906914893617021</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>1.62</v>
-      </c>
-      <c r="V4">
-        <v>0.01394148020654045</v>
-      </c>
-      <c r="W4">
-        <v>-0.220398593200469</v>
-      </c>
-      <c r="X4">
-        <v>0.07245421904070486</v>
-      </c>
-      <c r="Y4">
-        <v>-0.2928528122411738</v>
-      </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
-      <c r="AA4">
-        <v>-0.2280890804597701</v>
-      </c>
-      <c r="AB4">
-        <v>0.07245421904070486</v>
-      </c>
-      <c r="AC4">
-        <v>-0.300543299500475</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>-1.62</v>
-      </c>
-      <c r="AH4">
-        <v>0</v>
-      </c>
-      <c r="AI4">
-        <v>0</v>
-      </c>
-      <c r="AJ4">
-        <v>-0.01413859312270902</v>
-      </c>
-      <c r="AK4">
-        <v>-0.01483788239604323</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
         <v>0</v>
       </c>
     </row>
